--- a/unified_results.xlsx
+++ b/unified_results.xlsx
@@ -11,6 +11,10 @@
     <sheet name="ConstrainedGoToObjDoor_1c" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ConstrainedActionObjDoor_1c" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ConstrainedOpenDoor_1c" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ConstrainedOpenDoorsOrder_1c" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ConstrainedPickupDist_1c" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ConstrainedOpenDoorLoc_1c" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ConstrainedGoToOpen_1c" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +500,24 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100.22 ± 114.48</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.15</t>
         </is>
       </c>
     </row>
@@ -510,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +588,42 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>83.97 ± 92.64</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>82.48 ± 93.07</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
         </is>
@@ -582,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,6 +680,60 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>640.30 ± 439.96</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>517.33 ± 452.72</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>558.16 ± 458.09</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -636,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,6 +791,492 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>240.84 ± 271.17</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>212.99 ± 237.86</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>247.69 ± 275.11</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>293.85 ± 362.89</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>300.91 ± 374.92</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>289.23 ± 365.89</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>321.10 ± 392.30</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>345.11 ± 206.47</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>261.58 ± 204.36</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>244.58 ± 196.66</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>307.23 ± 214.62</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>465.45 ± 383.65</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>151.75 ± 236.80</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>167.25 ± 245.19</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>449.96 ± 387.56</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>17.92 ± 69.77</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>615.22 ± 452.14</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>17.68 ± 101.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>597.97 ± 454.91</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>19.36 ± 86.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>587.13 ± 459.90</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>14.42 ± 71.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>607.05 ± 462.55</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20.05 ± 97.29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/unified_results.xlsx
+++ b/unified_results.xlsx
@@ -15,6 +15,14 @@
     <sheet name="ConstrainedPickupDist_1c" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ConstrainedOpenDoorLoc_1c" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="ConstrainedGoToOpen_1c" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ConstrainedGoToObjDoor_2c" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ConstrainedGoToLocal_2c" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ConstrainedActionObjDoor_2c" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ConstrainedOpenDoor_2c" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ConstrainedOpenDoorsOrder_2c" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ConstrainedOpenDoorLoc_2c" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ConstrainedPickupDist_2c" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ConstrainedGoToOpen_2c" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,6 +534,744 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>124.64 ± 124.46</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>123.11 ± 126.15</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>123.50 ± 125.17</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>126.75 ± 123.38</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>627.51 ± 417.63</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>576.13 ± 460.04</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>598.82 ± 457.54</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>667.18 ± 416.30</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.24</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>273.79 ± 292.65</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>323.42 ± 325.84</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.51 ± 5.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>402.36 ± 356.28</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.50 ± 9.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>267.86 ± 281.21</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.06</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>341.03 ± 421.96</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>373.70 ± 450.41</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>402.02 ± 452.46</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>449.22 ± 475.81</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>463.60 ± 385.10</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>33.30 ± 90.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>499.66 ± 378.50</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>38.48 ± 89.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>210.48 ± 281.49</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>203.20 ± 283.74</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.06</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>413.08 ± 185.00</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>404.77 ± 186.39</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>284.33 ± 201.34</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>388.62 ± 197.09</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>607.50 ± 448.62</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>31.09 ± 117.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>564.25 ± 454.04</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>32.56 ± 113.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>605.69 ± 453.41</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>43.89 ± 144.74</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1280,4 +2026,112 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>85.10 ± 95.48</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>90.66 ± 101.59</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>105.79 ± 106.77</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>95.89 ± 101.21</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/unified_results.xlsx
+++ b/unified_results.xlsx
@@ -1188,7 +1188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1264,6 +1264,24 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>43.89 ± 144.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>612.36 ± 454.55</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>45.55 ± 140.64</t>
         </is>
       </c>
     </row>
